--- a/docs/Autopark/examples/autopark_audit_demo.xlsx
+++ b/docs/Autopark/examples/autopark_audit_demo.xlsx
@@ -18123,12 +18123,12 @@
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
-          <t>Один и тот же рейс не может быть учтён дважды — ни через второй путевой лист, ни через повторную постановку бензовоза на линию.</t>
+          <t>Один и тот же рейс не может быть учтён дважды — ни через второй путевой лист, ни через полностью повторённый документ.</t>
         </is>
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>Поиск повторов по ключам (бензовоз + дата) и (номер путевого листа) по всей популяции рейсов.</t>
+          <t>Поиск повторов по номеру путевого листа и по полному совпадению реквизитов (бензовоз, дата, водитель, нормативный пробег) по всей популяции рейсов. Два разных рейса одной машины за день отклонением не считаются.</t>
         </is>
       </c>
       <c r="E16" s="35" t="inlineStr">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="C647" s="33" t="inlineStr">
         <is>
-          <t>Ключ</t>
+          <t>Ключ повтора</t>
         </is>
       </c>
       <c r="D647" s="33" t="inlineStr">
@@ -35277,7 +35277,7 @@
       </c>
       <c r="C648" s="34" t="inlineStr">
         <is>
-          <t>AP-40732</t>
+          <t>путевой лист AP-40732</t>
         </is>
       </c>
       <c r="D648" s="46" t="n">
@@ -35300,7 +35300,7 @@
       </c>
       <c r="C649" s="40" t="inlineStr">
         <is>
-          <t>AP-42029</t>
+          <t>путевой лист AP-42029</t>
         </is>
       </c>
       <c r="D649" s="49" t="n">
@@ -35323,7 +35323,7 @@
       </c>
       <c r="C650" s="34" t="inlineStr">
         <is>
-          <t>AP-42881</t>
+          <t>путевой лист AP-42881</t>
         </is>
       </c>
       <c r="D650" s="46" t="n">

--- a/docs/Autopark/examples/autopark_audit_demo.xlsx
+++ b/docs/Autopark/examples/autopark_audit_demo.xlsx
@@ -16286,7 +16286,7 @@
       </c>
       <c r="E6" s="35" t="inlineStr">
         <is>
-          <t>При проверке 10576 объектов (100 % позиций с зафиксированными отгрузкой и приёмкой) выявлено 197 отклонений (1.86 %). Денежная оценка: 1 132 934.40 лея.</t>
+          <t>Проверено 10576 объектов (100 % позиций с зафиксированными отгрузкой и приёмкой), выявлено 197 отклонений (1.86 %). Денежная оценка: 1 132 934.40 лея.</t>
         </is>
       </c>
       <c r="F6" s="35" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>При проверке 3534 объектов (100 % рейсов с зафиксированной заправкой) выявлено 96 отклонений (2.72 %). Денежная оценка: 53 994.44 лея.</t>
+          <t>Проверено 3534 объекта (100 % рейсов с зафиксированной заправкой), выявлено 96 отклонений (2.72 %). Денежная оценка: 53 994.44 лея.</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="E8" s="35" t="inlineStr">
         <is>
-          <t>При проверке 77 объектов (100 % резервуаров сети) выявлено 6 отклонений (7.79 %).</t>
+          <t>Проверено 77 объектов (100 % резервуаров сети), выявлено 6 отклонений (7.79 %).</t>
         </is>
       </c>
       <c r="F8" s="35" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="E9" s="41" t="inlineStr">
         <is>
-          <t>При проверке 3534 объектов (100 % рейсов с зафиксированным фактическим пробегом) выявлено 151 отклонений (4.27 %). Денежная оценка: 30 259.60 лея.</t>
+          <t>Проверено 3534 объекта (100 % рейсов с зафиксированным фактическим пробегом), выявлено 151 отклонение (4.27 %). Денежная оценка: 30 259.60 леев.</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="E10" s="35" t="inlineStr">
         <is>
-          <t>При проверке 3534 объектов (100 % утверждённых рейсов с заполненными автором и утвердившим) выявлено 74 отклонений (2.09 %).</t>
+          <t>Проверено 3534 объекта (100 % утверждённых рейсов с заполненными автором и утвердившим), выявлено 74 отклонения (2.09 %).</t>
         </is>
       </c>
       <c r="F10" s="35" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="E11" s="41" t="inlineStr">
         <is>
-          <t>При проверке 91 объектов (100 % резервуаров и бензовозов) выявлено 2 отклонений (2.20 %).</t>
+          <t>Проверено 91 объект (100 % резервуаров и бензовозов), выявлено 2 отклонения (2.20 %).</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="E12" s="35" t="inlineStr">
         <is>
-          <t>При проверке 3515 объектов (100 % рейсов периода со статусом не «черновик») выявлено 18 отклонений (0.51 %). Денежная оценка: 2 622.71 лея.</t>
+          <t>Проверено 3515 объектов (100 % рейсов периода со статусом не «черновик»), выявлено 18 отклонений (0.51 %). Денежная оценка: 2 622.71 лея.</t>
         </is>
       </c>
       <c r="F12" s="35" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="E13" s="41" t="inlineStr">
         <is>
-          <t>При проверке 10576 объектов (100 % позиций рейсов с назначенным отсеком) выявлено 10 отклонений (0.09 %).</t>
+          <t>Проверено 10576 объектов (100 % позиций рейсов с назначенным отсеком), выявлено 10 отклонений (0.09 %).</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="E14" s="35" t="inlineStr">
         <is>
-          <t>При проверке 10576 объектов (100 % позиций с зафиксированным объёмом) выявлено 5 отклонений (0.05 %).</t>
+          <t>Проверено 10576 объектов (100 % позиций с зафиксированным объёмом), выявлено 5 отклонений (0.05 %).</t>
         </is>
       </c>
       <c r="F14" s="35" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="E15" s="41" t="inlineStr">
         <is>
-          <t>При проверке 3534 объектов (100 % рейсов периода со статусом не «черновик») выявлено 19 отклонений (0.54 %).</t>
+          <t>Проверено 3534 объекта (100 % рейсов периода со статусом не «черновик»), выявлено 19 отклонений (0.54 %).</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="E16" s="35" t="inlineStr">
         <is>
-          <t>При проверке 3534 объектов (100 % рейсов с журналом статусов) выявлено 35 отклонений (0.99 %).</t>
+          <t>Проверено 3534 объекта (100 % рейсов с журналом статусов), выявлено 35 отклонений (0.99 %).</t>
         </is>
       </c>
       <c r="F16" s="35" t="inlineStr">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="E17" s="41" t="inlineStr">
         <is>
-          <t>При проверке 3534 объектов (100 % рейсов периода со статусом не «черновик») выявлено 3 отклонений (0.08 %).</t>
+          <t>Проверено 3534 объекта (100 % рейсов периода со статусом не «черновик»), выявлено 3 отклонения (0.08 %).</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
